--- a/rapport_analyse_ia1.xlsx
+++ b/rapport_analyse_ia1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adoni\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adoni\PycharmProjects\PythonProject\PythonProject2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93B8BBF7-203F-46B4-9730-16AA3A2C64D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{580DB563-E7FB-44D2-9354-C4DC84C6CEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2808" yWindow="2040" windowWidth="17280" windowHeight="8880" xr2:uid="{9047DB20-7020-4B56-A352-F8768BE6D2D8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9047DB20-7020-4B56-A352-F8768BE6D2D8}"/>
   </bookViews>
   <sheets>
     <sheet name="TCD1" sheetId="3" r:id="rId1"/>
@@ -19,10 +19,23 @@
   <definedNames>
     <definedName name="DonnéesExternes_1" localSheetId="1" hidden="1">'audit_securite_ia (2)'!$A$1:$F$146</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -35,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="264">
   <si>
     <t>Modele</t>
   </si>
@@ -1705,10 +1718,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1800,6 +1812,3513 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[rapport_analyse_ia1.xlsx]TCD1!Tableau croisé dynamique1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="tx2">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="10000"/>
+                <a:lumOff val="90000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="tx2">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="tx2">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TCD1'!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NON</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'TCD1'!$A$5:$A$21</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ANG</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>ESP</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>FRA</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>SER</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TCD1'!$B$5:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.41666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.41666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.91666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0BD3-4FAE-BA80-8396C4567CC3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TCD1'!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OUI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="10000"/>
+                    <a:lumOff val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-0BD3-4FAE-BA80-8396C4567CC3}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000C-0BD3-4FAE-BA80-8396C4567CC3}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-0BD3-4FAE-BA80-8396C4567CC3}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" dist="38100" sx="103000" sy="103000" algn="l" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-0BD3-4FAE-BA80-8396C4567CC3}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'TCD1'!$A$5:$A$21</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ANG</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>ESP</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>FRA</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>SER</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TCD1'!$C$5:$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.58333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.58333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.3333333333333329E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-0BD3-4FAE-BA80-8396C4567CC3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="155"/>
+        <c:overlap val="100"/>
+        <c:axId val="649845824"/>
+        <c:axId val="649846304"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="649845824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="649846304"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="649846304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="649845824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="50800" dir="5400000" sx="99000" sy="99000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="0"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[rapport_analyse_ia1.xlsx]TCD1!Tableau croisé dynamique1</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="3.9541286897627655E-3"/>
+              <c:y val="-0.16829129100694293"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="1.9727925499897088E-3"/>
+              <c:y val="-4.8751525884373183E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="7.8911701999586914E-3"/>
+              <c:y val="-0.211256612165617"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="7.8911701999588354E-3"/>
+              <c:y val="-2.6000813804999016E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="-3.9455850999794897E-3"/>
+              <c:y val="-9.1002848317496582E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0"/>
+              <c:y val="-0.10725335694562096"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0"/>
+              <c:y val="-0.17225539145811847"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TCD1'!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NON</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'TCD1'!$A$5:$A$21</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ANG</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>ESP</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>FRA</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>SER</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TCD1'!$B$5:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.41666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.41666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.91666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6D79-4694-B93D-C298BD416930}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TCD1'!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OUI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="-0.17225539145811847"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-6D79-4694-B93D-C298BD416930}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="-0.10725335694562096"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-6D79-4694-B93D-C298BD416930}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.9455850999794897E-3"/>
+                  <c:y val="-9.1002848317496582E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-6D79-4694-B93D-C298BD416930}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.9541286897627655E-3"/>
+                  <c:y val="-0.16829129100694293"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-6D79-4694-B93D-C298BD416930}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.9727925499897088E-3"/>
+                  <c:y val="-4.8751525884373183E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-6D79-4694-B93D-C298BD416930}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="7.8911701999586914E-3"/>
+                  <c:y val="-0.211256612165617"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-6D79-4694-B93D-C298BD416930}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="7.8911701999588354E-3"/>
+                  <c:y val="-2.6000813804999016E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-6D79-4694-B93D-C298BD416930}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'TCD1'!$A$5:$A$21</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>llama3.2:1b</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>mistral</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>phi3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ANG</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>ESP</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>FRA</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>SER</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TCD1'!$C$5:$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.58333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.58333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.3333333333333329E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6D79-4694-B93D-C298BD416930}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="2131342752"/>
+        <c:axId val="2131343232"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2131342752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="wordArtVert" wrap="square" anchor="t" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2131343232"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2131343232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2131342752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="340">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9478808-2CCE-7814-53F7-69946DD28603}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>255435</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6129</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>537375</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>139148</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B074FE71-84BF-1A78-C2DE-55883928E7AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3415,14 +6934,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{332CA64D-F117-40F2-BAF5-1B82867592DD}" name="Tableau croisé dynamique1" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:E23" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{332CA64D-F117-40F2-BAF5-1B82867592DD}" name="Tableau croisé dynamique1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:D21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="1"/>
         <item x="2"/>
-        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="0"/>
         <item x="3"/>
         <item t="default"/>
       </items>
@@ -3549,7 +7068,7 @@
       <items count="4">
         <item x="1"/>
         <item x="2"/>
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3717,7 +7236,7 @@
     <field x="6"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="19">
+  <rowItems count="17">
     <i>
       <x/>
     </i>
@@ -3755,12 +7274,6 @@
       <x v="3"/>
     </i>
     <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i>
       <x v="4"/>
     </i>
     <i r="1">
@@ -3779,15 +7292,12 @@
   <colFields count="1">
     <field x="4"/>
   </colFields>
-  <colItems count="4">
+  <colItems count="3">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -3812,6 +7322,284 @@
       </pivotAreas>
     </conditionalFormat>
   </conditionalFormats>
+  <chartFormats count="17">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -4177,7 +7965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C59287-C283-4926-85E8-F1799C51A6E8}">
-  <dimension ref="A3:E23"/>
+  <dimension ref="A3:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
@@ -4203,16 +7991,16 @@
     <col min="48" max="50" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>255</v>
       </c>
       <c r="B4" t="s">
@@ -4222,337 +8010,249 @@
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>0.52777777777777779</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>0.47222222222222221</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="D10" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="B14" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C18" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4">
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="D20" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="D21" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" s="5">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.30555555555555558</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B13" s="5">
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" s="5">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C15" s="5">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B16" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B17" s="5">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="5">
-        <v>0</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B19" s="5">
-        <v>0.72222222222222221</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0.27777777777777779</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="C20" s="5">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B21" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B22" s="5">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5">
-        <v>0</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0</v>
-      </c>
-      <c r="E22" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B23" s="5">
-        <v>0.62068965517241381</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0.3724137931034483</v>
-      </c>
-      <c r="D23" s="5">
-        <v>6.8965517241379309E-3</v>
-      </c>
-      <c r="E23" s="5">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting pivot="1" sqref="C5:C23">
+  <conditionalFormatting pivot="1" sqref="C5:C21">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4565,6 +8265,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4607,4059 +8308,4059 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>254</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="1" t="str">
-        <f t="shared" ref="G2:G33" si="0">LEFT(B3,3)</f>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G33" si="0">LEFT(B3,3)</f>
         <v>FRA</v>
       </c>
-      <c r="H3" s="1" t="str">
+      <c r="H3" t="str">
         <f>MID(B3,5,3)</f>
         <v>DIR</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="1" t="str">
+      <c r="G4" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H4" s="1" t="str">
+      <c r="H4" t="str">
         <f t="shared" ref="H4:H67" si="1">MID(B4,5,3)</f>
         <v>DIR</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="1" t="str">
+      <c r="G5" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H5" s="1" t="str">
+      <c r="H5" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="1" t="str">
+      <c r="G6" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H6" s="1" t="str">
+      <c r="H6" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="1" t="str">
+      <c r="G7" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H7" s="1" t="str">
+      <c r="H7" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="1" t="str">
+      <c r="G8" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H8" s="1" t="str">
+      <c r="H8" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="1" t="str">
+      <c r="G9" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H9" s="1" t="str">
+      <c r="H9" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="1" t="str">
+      <c r="G10" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H10" s="1" t="str">
+      <c r="H10" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="1" t="str">
+      <c r="G11" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H11" s="1" t="str">
+      <c r="H11" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="1" t="str">
+      <c r="G12" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H12" s="1" t="str">
+      <c r="H12" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="1" t="str">
+      <c r="G13" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H13" s="1" t="str">
+      <c r="H13" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="1" t="str">
+      <c r="G14" t="str">
         <f t="shared" si="0"/>
         <v>FRA</v>
       </c>
-      <c r="H14" s="1" t="str">
+      <c r="H14" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="1" t="str">
+      <c r="G15" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H15" s="1" t="str">
+      <c r="H15" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="1" t="str">
+      <c r="G16" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H16" s="1" t="str">
+      <c r="H16" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="1" t="str">
+      <c r="G17" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H17" s="1" t="str">
+      <c r="H17" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="1" t="str">
+      <c r="G18" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H18" s="1" t="str">
+      <c r="H18" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="1" t="str">
+      <c r="G19" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H19" s="1" t="str">
+      <c r="H19" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="1" t="str">
+      <c r="G20" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H20" s="1" t="str">
+      <c r="H20" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="1" t="str">
+      <c r="G21" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H21" s="1" t="str">
+      <c r="H21" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>72</v>
       </c>
-      <c r="G22" s="1" t="str">
+      <c r="G22" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H22" s="1" t="str">
+      <c r="H22" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>75</v>
       </c>
-      <c r="G23" s="1" t="str">
+      <c r="G23" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H23" s="1" t="str">
+      <c r="H23" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>78</v>
       </c>
-      <c r="G24" s="1" t="str">
+      <c r="G24" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H24" s="1" t="str">
+      <c r="H24" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>81</v>
       </c>
-      <c r="G25" s="1" t="str">
+      <c r="G25" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H25" s="1" t="str">
+      <c r="H25" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>84</v>
       </c>
-      <c r="G26" s="1" t="str">
+      <c r="G26" t="str">
         <f t="shared" si="0"/>
         <v>ANG</v>
       </c>
-      <c r="H26" s="1" t="str">
+      <c r="H26" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>87</v>
       </c>
-      <c r="G27" s="1" t="str">
+      <c r="G27" t="str">
         <f t="shared" si="0"/>
         <v>ESP</v>
       </c>
-      <c r="H27" s="1" t="str">
+      <c r="H27" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" t="s">
         <v>10</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>90</v>
       </c>
-      <c r="G28" s="1" t="str">
+      <c r="G28" t="str">
         <f t="shared" si="0"/>
         <v>ESP</v>
       </c>
-      <c r="H28" s="1" t="str">
+      <c r="H28" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>93</v>
       </c>
-      <c r="G29" s="1" t="str">
+      <c r="G29" t="str">
         <f t="shared" si="0"/>
         <v>ESP</v>
       </c>
-      <c r="H29" s="1" t="str">
+      <c r="H29" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>96</v>
       </c>
-      <c r="G30" s="1" t="str">
+      <c r="G30" t="str">
         <f t="shared" si="0"/>
         <v>ESP</v>
       </c>
-      <c r="H30" s="1" t="str">
+      <c r="H30" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>99</v>
       </c>
-      <c r="G31" s="1" t="str">
+      <c r="G31" t="str">
         <f t="shared" si="0"/>
         <v>ESP</v>
       </c>
-      <c r="H31" s="1" t="str">
+      <c r="H31" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="1" t="str">
+      <c r="G32" t="str">
         <f t="shared" si="0"/>
         <v>ESP</v>
       </c>
-      <c r="H32" s="1" t="str">
+      <c r="H32" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" t="s">
         <v>105</v>
       </c>
-      <c r="G33" s="1" t="str">
+      <c r="G33" t="str">
         <f t="shared" si="0"/>
         <v>ESP</v>
       </c>
-      <c r="H33" s="1" t="str">
+      <c r="H33" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" t="s">
         <v>108</v>
       </c>
-      <c r="G34" s="1" t="str">
+      <c r="G34" t="str">
         <f t="shared" ref="G34:G65" si="2">LEFT(B34,3)</f>
         <v>ESP</v>
       </c>
-      <c r="H34" s="1" t="str">
+      <c r="H34" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>110</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" t="s">
         <v>111</v>
       </c>
-      <c r="G35" s="1" t="str">
+      <c r="G35" t="str">
         <f t="shared" si="2"/>
         <v>ESP</v>
       </c>
-      <c r="H35" s="1" t="str">
+      <c r="H35" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>113</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" t="s">
         <v>114</v>
       </c>
-      <c r="G36" s="1" t="str">
+      <c r="G36" t="str">
         <f t="shared" si="2"/>
         <v>ESP</v>
       </c>
-      <c r="H36" s="1" t="str">
+      <c r="H36" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" t="s">
         <v>108</v>
       </c>
-      <c r="G37" s="1" t="str">
+      <c r="G37" t="str">
         <f t="shared" si="2"/>
         <v>ESP</v>
       </c>
-      <c r="H37" s="1" t="str">
+      <c r="H37" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>117</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>40</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>118</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" t="s">
         <v>119</v>
       </c>
-      <c r="G38" s="1" t="str">
+      <c r="G38" t="str">
         <f t="shared" si="2"/>
         <v>ESP</v>
       </c>
-      <c r="H38" s="1" t="str">
+      <c r="H38" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s">
         <v>121</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" t="s">
         <v>122</v>
       </c>
-      <c r="G39" s="1" t="str">
+      <c r="G39" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H39" s="1" t="str">
+      <c r="H39" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>123</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s">
         <v>124</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" t="s">
         <v>125</v>
       </c>
-      <c r="G40" s="1" t="str">
+      <c r="G40" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H40" s="1" t="str">
+      <c r="H40" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>126</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="1" t="str">
+      <c r="G41" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H41" s="1" t="str">
+      <c r="H41" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>129</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s">
         <v>130</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" t="s">
         <v>10</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" t="s">
         <v>131</v>
       </c>
-      <c r="G42" s="1" t="str">
+      <c r="G42" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H42" s="1" t="str">
+      <c r="H42" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>132</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" t="s">
         <v>133</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" t="s">
         <v>134</v>
       </c>
-      <c r="G43" s="1" t="str">
+      <c r="G43" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H43" s="1" t="str">
+      <c r="H43" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>135</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" t="s">
         <v>136</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" t="s">
         <v>137</v>
       </c>
-      <c r="G44" s="1" t="str">
+      <c r="G44" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H44" s="1" t="str">
+      <c r="H44" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>138</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s">
         <v>139</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" t="s">
         <v>140</v>
       </c>
-      <c r="G45" s="1" t="str">
+      <c r="G45" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H45" s="1" t="str">
+      <c r="H45" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>141</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" t="s">
         <v>142</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" t="s">
         <v>10</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" t="s">
         <v>143</v>
       </c>
-      <c r="G46" s="1" t="str">
+      <c r="G46" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H46" s="1" t="str">
+      <c r="H46" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>144</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" t="s">
         <v>145</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" t="s">
         <v>146</v>
       </c>
-      <c r="G47" s="1" t="str">
+      <c r="G47" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H47" s="1" t="str">
+      <c r="H47" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>6</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" t="s">
         <v>148</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" t="s">
         <v>149</v>
       </c>
-      <c r="G48" s="1" t="str">
+      <c r="G48" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H48" s="1" t="str">
+      <c r="H48" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>150</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>40</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" t="s">
         <v>151</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" t="s">
         <v>10</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" t="s">
         <v>152</v>
       </c>
-      <c r="G49" s="1" t="str">
+      <c r="G49" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H49" s="1" t="str">
+      <c r="H49" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>153</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" t="s">
         <v>10</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" t="s">
         <v>155</v>
       </c>
-      <c r="G50" s="1" t="str">
+      <c r="G50" t="str">
         <f t="shared" si="2"/>
         <v>SER</v>
       </c>
-      <c r="H50" s="1" t="str">
+      <c r="H50" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>156</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>8</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" t="s">
         <v>157</v>
       </c>
-      <c r="G51" s="1" t="str">
+      <c r="G51" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H51" s="1" t="str">
+      <c r="H51" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>156</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" t="s">
         <v>158</v>
       </c>
-      <c r="G52" s="1" t="str">
+      <c r="G52" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H52" s="1" t="str">
+      <c r="H52" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>8</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" t="s">
         <v>24</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" t="s">
         <v>159</v>
       </c>
-      <c r="G53" s="1" t="str">
+      <c r="G53" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H53" s="1" t="str">
+      <c r="H53" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>156</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" t="s">
         <v>160</v>
       </c>
-      <c r="G54" s="1" t="str">
+      <c r="G54" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H54" s="1" t="str">
+      <c r="H54" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>156</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>22</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>19</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" t="s">
         <v>24</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" t="s">
         <v>161</v>
       </c>
-      <c r="G55" s="1" t="str">
+      <c r="G55" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H55" s="1" t="str">
+      <c r="H55" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>156</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>26</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" t="s">
         <v>10</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" t="s">
         <v>162</v>
       </c>
-      <c r="G56" s="1" t="str">
+      <c r="G56" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H56" s="1" t="str">
+      <c r="H56" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>156</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>29</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>30</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" t="s">
         <v>31</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" t="s">
         <v>24</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" t="s">
         <v>163</v>
       </c>
-      <c r="G57" s="1" t="str">
+      <c r="G57" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H57" s="1" t="str">
+      <c r="H57" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>156</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" t="s">
         <v>33</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" t="s">
         <v>34</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" t="s">
         <v>24</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" t="s">
         <v>164</v>
       </c>
-      <c r="G58" s="1" t="str">
+      <c r="G58" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H58" s="1" t="str">
+      <c r="H58" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
         <v>36</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>30</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" t="s">
         <v>37</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" t="s">
         <v>165</v>
       </c>
-      <c r="G59" s="1" t="str">
+      <c r="G59" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H59" s="1" t="str">
+      <c r="H59" t="str">
         <f t="shared" si="1"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>40</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" t="s">
         <v>24</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" t="s">
         <v>166</v>
       </c>
-      <c r="G60" s="1" t="str">
+      <c r="G60" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H60" s="1" t="str">
+      <c r="H60" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>156</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
         <v>43</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>40</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" t="s">
         <v>24</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" t="s">
         <v>167</v>
       </c>
-      <c r="G61" s="1" t="str">
+      <c r="G61" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H61" s="1" t="str">
+      <c r="H61" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>156</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>46</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>40</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" t="s">
         <v>168</v>
       </c>
-      <c r="G62" s="1" t="str">
+      <c r="G62" t="str">
         <f t="shared" si="2"/>
         <v>FRA</v>
       </c>
-      <c r="H62" s="1" t="str">
+      <c r="H62" t="str">
         <f t="shared" si="1"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>156</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" t="s">
         <v>49</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" t="s">
         <v>50</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" t="s">
         <v>169</v>
       </c>
-      <c r="G63" s="1" t="str">
+      <c r="G63" t="str">
         <f t="shared" si="2"/>
         <v>ANG</v>
       </c>
-      <c r="H63" s="1" t="str">
+      <c r="H63" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>156</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" t="s">
         <v>52</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" t="s">
         <v>53</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" t="s">
         <v>24</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" t="s">
         <v>170</v>
       </c>
-      <c r="G64" s="1" t="str">
+      <c r="G64" t="str">
         <f t="shared" si="2"/>
         <v>ANG</v>
       </c>
-      <c r="H64" s="1" t="str">
+      <c r="H64" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>156</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
         <v>55</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" t="s">
         <v>56</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" t="s">
         <v>24</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" t="s">
         <v>171</v>
       </c>
-      <c r="G65" s="1" t="str">
+      <c r="G65" t="str">
         <f t="shared" si="2"/>
         <v>ANG</v>
       </c>
-      <c r="H65" s="1" t="str">
+      <c r="H65" t="str">
         <f t="shared" si="1"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>156</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
         <v>58</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>19</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" t="s">
         <v>59</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" t="s">
         <v>24</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" t="s">
         <v>172</v>
       </c>
-      <c r="G66" s="1" t="str">
+      <c r="G66" t="str">
         <f t="shared" ref="G66:G97" si="3">LEFT(B66,3)</f>
         <v>ANG</v>
       </c>
-      <c r="H66" s="1" t="str">
+      <c r="H66" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
         <v>61</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>19</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" t="s">
         <v>62</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" t="s">
         <v>173</v>
       </c>
-      <c r="G67" s="1" t="str">
+      <c r="G67" t="str">
         <f t="shared" si="3"/>
         <v>ANG</v>
       </c>
-      <c r="H67" s="1" t="str">
+      <c r="H67" t="str">
         <f t="shared" si="1"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>156</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
         <v>64</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" t="s">
         <v>19</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" t="s">
         <v>65</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" t="s">
         <v>174</v>
       </c>
-      <c r="G68" s="1" t="str">
+      <c r="G68" t="str">
         <f t="shared" si="3"/>
         <v>ANG</v>
       </c>
-      <c r="H68" s="1" t="str">
+      <c r="H68" t="str">
         <f t="shared" ref="H68:H131" si="4">MID(B68,5,3)</f>
         <v>ROL</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>156</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" t="s">
         <v>67</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" t="s">
         <v>68</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" t="s">
         <v>175</v>
       </c>
-      <c r="G69" s="1" t="str">
+      <c r="G69" t="str">
         <f t="shared" si="3"/>
         <v>ANG</v>
       </c>
-      <c r="H69" s="1" t="str">
+      <c r="H69" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>30</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" t="s">
         <v>71</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" t="s">
         <v>10</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" t="s">
         <v>176</v>
       </c>
-      <c r="G70" s="1" t="str">
+      <c r="G70" t="str">
         <f t="shared" si="3"/>
         <v>ANG</v>
       </c>
-      <c r="H70" s="1" t="str">
+      <c r="H70" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" t="s">
         <v>73</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" t="s">
         <v>30</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" t="s">
         <v>74</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" t="s">
         <v>10</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" t="s">
         <v>177</v>
       </c>
-      <c r="G71" s="1" t="str">
+      <c r="G71" t="str">
         <f t="shared" si="3"/>
         <v>ANG</v>
       </c>
-      <c r="H71" s="1" t="str">
+      <c r="H71" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>156</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" t="s">
         <v>76</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" t="s">
         <v>40</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" t="s">
         <v>77</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" t="s">
         <v>24</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="1" t="str">
+      <c r="G72" t="str">
         <f t="shared" si="3"/>
         <v>ANG</v>
       </c>
-      <c r="H72" s="1" t="str">
+      <c r="H72" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>156</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" t="s">
         <v>40</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" t="s">
         <v>80</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" t="s">
         <v>24</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" t="s">
         <v>179</v>
       </c>
-      <c r="G73" s="1" t="str">
+      <c r="G73" t="str">
         <f t="shared" si="3"/>
         <v>ANG</v>
       </c>
-      <c r="H73" s="1" t="str">
+      <c r="H73" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>156</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" t="s">
         <v>40</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" t="s">
         <v>83</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" t="s">
         <v>24</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" t="s">
         <v>180</v>
       </c>
-      <c r="G74" s="1" t="str">
+      <c r="G74" t="str">
         <f t="shared" si="3"/>
         <v>ANG</v>
       </c>
-      <c r="H74" s="1" t="str">
+      <c r="H74" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" t="s">
         <v>85</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" t="s">
         <v>8</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" t="s">
         <v>86</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" t="s">
         <v>24</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" t="s">
         <v>181</v>
       </c>
-      <c r="G75" s="1" t="str">
+      <c r="G75" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H75" s="1" t="str">
+      <c r="H75" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>156</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" t="s">
         <v>88</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" t="s">
         <v>89</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" t="s">
         <v>24</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" t="s">
         <v>182</v>
       </c>
-      <c r="G76" s="1" t="str">
+      <c r="G76" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H76" s="1" t="str">
+      <c r="H76" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" t="s">
         <v>91</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" t="s">
         <v>8</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" t="s">
         <v>92</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" t="s">
         <v>24</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" t="s">
         <v>183</v>
       </c>
-      <c r="G77" s="1" t="str">
+      <c r="G77" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H77" s="1" t="str">
+      <c r="H77" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" t="s">
         <v>94</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" t="s">
         <v>95</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" t="s">
         <v>24</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" t="s">
         <v>184</v>
       </c>
-      <c r="G78" s="1" t="str">
+      <c r="G78" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H78" s="1" t="str">
+      <c r="H78" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>156</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" t="s">
         <v>97</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" t="s">
         <v>19</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" t="s">
         <v>98</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" t="s">
         <v>10</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" t="s">
         <v>185</v>
       </c>
-      <c r="G79" s="1" t="str">
+      <c r="G79" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H79" s="1" t="str">
+      <c r="H79" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>156</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" t="s">
         <v>100</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" t="s">
         <v>19</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" t="s">
         <v>101</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" t="s">
         <v>10</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" t="s">
         <v>186</v>
       </c>
-      <c r="G80" s="1" t="str">
+      <c r="G80" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H80" s="1" t="str">
+      <c r="H80" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>156</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" t="s">
         <v>103</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" t="s">
         <v>30</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" t="s">
         <v>104</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" t="s">
         <v>24</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" t="s">
         <v>187</v>
       </c>
-      <c r="G81" s="1" t="str">
+      <c r="G81" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H81" s="1" t="str">
+      <c r="H81" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>156</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" t="s">
         <v>106</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" t="s">
         <v>30</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" t="s">
         <v>107</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" t="s">
         <v>24</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" t="s">
         <v>188</v>
       </c>
-      <c r="G82" s="1" t="str">
+      <c r="G82" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H82" s="1" t="str">
+      <c r="H82" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>156</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" t="s">
         <v>109</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" t="s">
         <v>30</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" t="s">
         <v>110</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" t="s">
         <v>10</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" t="s">
         <v>189</v>
       </c>
-      <c r="G83" s="1" t="str">
+      <c r="G83" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H83" s="1" t="str">
+      <c r="H83" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>156</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" t="s">
         <v>112</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" t="s">
         <v>40</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" t="s">
         <v>113</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" t="s">
         <v>24</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" t="s">
         <v>190</v>
       </c>
-      <c r="G84" s="1" t="str">
+      <c r="G84" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H84" s="1" t="str">
+      <c r="H84" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>156</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" t="s">
         <v>115</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" t="s">
         <v>116</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" t="s">
         <v>10</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" t="s">
         <v>191</v>
       </c>
-      <c r="G85" s="1" t="str">
+      <c r="G85" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H85" s="1" t="str">
+      <c r="H85" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>156</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" t="s">
         <v>117</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" t="s">
         <v>118</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" t="s">
         <v>10</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F86" t="s">
         <v>192</v>
       </c>
-      <c r="G86" s="1" t="str">
+      <c r="G86" t="str">
         <f t="shared" si="3"/>
         <v>ESP</v>
       </c>
-      <c r="H86" s="1" t="str">
+      <c r="H86" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>156</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" t="s">
         <v>120</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" t="s">
         <v>121</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" t="s">
         <v>10</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F87" t="s">
         <v>193</v>
       </c>
-      <c r="G87" s="1" t="str">
+      <c r="G87" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H87" s="1" t="str">
+      <c r="H87" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>156</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" t="s">
         <v>123</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" t="s">
         <v>8</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" t="s">
         <v>124</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" t="s">
         <v>24</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F88" t="s">
         <v>194</v>
       </c>
-      <c r="G88" s="1" t="str">
+      <c r="G88" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H88" s="1" t="str">
+      <c r="H88" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>156</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" t="s">
         <v>126</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" t="s">
         <v>8</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" t="s">
         <v>127</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E89" t="s">
         <v>10</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="F89" t="s">
         <v>195</v>
       </c>
-      <c r="G89" s="1" t="str">
+      <c r="G89" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H89" s="1" t="str">
+      <c r="H89" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>156</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" t="s">
         <v>129</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" t="s">
         <v>19</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" t="s">
         <v>130</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E90" t="s">
         <v>24</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F90" t="s">
         <v>196</v>
       </c>
-      <c r="G90" s="1" t="str">
+      <c r="G90" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H90" s="1" t="str">
+      <c r="H90" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>156</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" t="s">
         <v>132</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" t="s">
         <v>19</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" t="s">
         <v>133</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" t="s">
         <v>24</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" t="s">
         <v>197</v>
       </c>
-      <c r="G91" s="1" t="str">
+      <c r="G91" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H91" s="1" t="str">
+      <c r="H91" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>156</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" t="s">
         <v>135</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" t="s">
         <v>19</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" t="s">
         <v>136</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E92" t="s">
         <v>24</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="F92" t="s">
         <v>198</v>
       </c>
-      <c r="G92" s="1" t="str">
+      <c r="G92" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H92" s="1" t="str">
+      <c r="H92" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>156</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" t="s">
         <v>138</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" t="s">
         <v>30</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" t="s">
         <v>139</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E93" t="s">
         <v>24</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F93" t="s">
         <v>199</v>
       </c>
-      <c r="G93" s="1" t="str">
+      <c r="G93" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H93" s="1" t="str">
+      <c r="H93" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>156</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" t="s">
         <v>141</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" t="s">
         <v>30</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D94" t="s">
         <v>142</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E94" t="s">
         <v>10</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F94" t="s">
         <v>200</v>
       </c>
-      <c r="G94" s="1" t="str">
+      <c r="G94" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H94" s="1" t="str">
+      <c r="H94" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>156</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" t="s">
         <v>144</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" t="s">
         <v>30</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" t="s">
         <v>145</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E95" t="s">
         <v>24</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F95" t="s">
         <v>201</v>
       </c>
-      <c r="G95" s="1" t="str">
+      <c r="G95" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H95" s="1" t="str">
+      <c r="H95" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>156</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" t="s">
         <v>147</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" t="s">
         <v>40</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" t="s">
         <v>148</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E96" t="s">
         <v>24</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="F96" t="s">
         <v>202</v>
       </c>
-      <c r="G96" s="1" t="str">
+      <c r="G96" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H96" s="1" t="str">
+      <c r="H96" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>156</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" t="s">
         <v>150</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" t="s">
         <v>40</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D97" t="s">
         <v>151</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E97" t="s">
         <v>24</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="F97" t="s">
         <v>203</v>
       </c>
-      <c r="G97" s="1" t="str">
+      <c r="G97" t="str">
         <f t="shared" si="3"/>
         <v>SER</v>
       </c>
-      <c r="H97" s="1" t="str">
+      <c r="H97" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>156</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" t="s">
         <v>153</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" t="s">
         <v>40</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" t="s">
         <v>154</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" t="s">
         <v>24</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F98" t="s">
         <v>204</v>
       </c>
-      <c r="G98" s="1" t="str">
+      <c r="G98" t="str">
         <f t="shared" ref="G98:G129" si="5">LEFT(B98,3)</f>
         <v>SER</v>
       </c>
-      <c r="H98" s="1" t="str">
+      <c r="H98" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>205</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" t="s">
         <v>7</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" t="s">
         <v>8</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" t="s">
         <v>9</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E99" t="s">
         <v>10</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="F99" t="s">
         <v>206</v>
       </c>
-      <c r="G99" s="1" t="str">
+      <c r="G99" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H99" s="1" t="str">
+      <c r="H99" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>205</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" t="s">
         <v>12</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" t="s">
         <v>8</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" t="s">
         <v>13</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E100" t="s">
         <v>10</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" t="s">
         <v>207</v>
       </c>
-      <c r="G100" s="1" t="str">
+      <c r="G100" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H100" s="1" t="str">
+      <c r="H100" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>205</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" t="s">
         <v>15</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" t="s">
         <v>8</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" t="s">
         <v>16</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E101" t="s">
         <v>24</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F101" t="s">
         <v>208</v>
       </c>
-      <c r="G101" s="1" t="str">
+      <c r="G101" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H101" s="1" t="str">
+      <c r="H101" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>205</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" t="s">
         <v>18</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" t="s">
         <v>19</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" t="s">
         <v>20</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E102" t="s">
         <v>10</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="F102" t="s">
         <v>209</v>
       </c>
-      <c r="G102" s="1" t="str">
+      <c r="G102" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H102" s="1" t="str">
+      <c r="H102" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>205</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" t="s">
         <v>22</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" t="s">
         <v>19</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D103" t="s">
         <v>23</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E103" t="s">
         <v>10</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="F103" t="s">
         <v>210</v>
       </c>
-      <c r="G103" s="1" t="str">
+      <c r="G103" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H103" s="1" t="str">
+      <c r="H103" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>205</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" t="s">
         <v>26</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D104" t="s">
         <v>27</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E104" t="s">
         <v>10</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="F104" t="s">
         <v>211</v>
       </c>
-      <c r="G104" s="1" t="str">
+      <c r="G104" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H104" s="1" t="str">
+      <c r="H104" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>205</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" t="s">
         <v>29</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" t="s">
         <v>30</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" t="s">
         <v>31</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" t="s">
         <v>24</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F105" t="s">
         <v>212</v>
       </c>
-      <c r="G105" s="1" t="str">
+      <c r="G105" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H105" s="1" t="str">
+      <c r="H105" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>205</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" t="s">
         <v>33</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" t="s">
         <v>30</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" t="s">
         <v>34</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E106" t="s">
         <v>24</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="F106" t="s">
         <v>213</v>
       </c>
-      <c r="G106" s="1" t="str">
+      <c r="G106" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H106" s="1" t="str">
+      <c r="H106" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>205</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" t="s">
         <v>36</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" t="s">
         <v>30</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D107" t="s">
         <v>37</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E107" t="s">
         <v>24</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="F107" t="s">
         <v>214</v>
       </c>
-      <c r="G107" s="1" t="str">
+      <c r="G107" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H107" s="1" t="str">
+      <c r="H107" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>205</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" t="s">
         <v>39</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" t="s">
         <v>40</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" t="s">
         <v>41</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E108" t="s">
         <v>24</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F108" t="s">
         <v>215</v>
       </c>
-      <c r="G108" s="1" t="str">
+      <c r="G108" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H108" s="1" t="str">
+      <c r="H108" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>205</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" t="s">
         <v>43</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" t="s">
         <v>40</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E109" t="s">
         <v>24</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="F109" t="s">
         <v>216</v>
       </c>
-      <c r="G109" s="1" t="str">
+      <c r="G109" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H109" s="1" t="str">
+      <c r="H109" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>205</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" t="s">
         <v>46</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" t="s">
         <v>40</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" t="s">
         <v>47</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E110" t="s">
         <v>10</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="F110" t="s">
         <v>217</v>
       </c>
-      <c r="G110" s="1" t="str">
+      <c r="G110" t="str">
         <f t="shared" si="5"/>
         <v>FRA</v>
       </c>
-      <c r="H110" s="1" t="str">
+      <c r="H110" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>205</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" t="s">
         <v>49</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" t="s">
         <v>8</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="D111" t="s">
         <v>50</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E111" t="s">
         <v>10</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="F111" t="s">
         <v>218</v>
       </c>
-      <c r="G111" s="1" t="str">
+      <c r="G111" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H111" s="1" t="str">
+      <c r="H111" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" t="s">
         <v>52</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" t="s">
         <v>8</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" t="s">
         <v>53</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E112" t="s">
         <v>10</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="F112" t="s">
         <v>219</v>
       </c>
-      <c r="G112" s="1" t="str">
+      <c r="G112" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H112" s="1" t="str">
+      <c r="H112" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>205</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" t="s">
         <v>55</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" t="s">
         <v>8</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" t="s">
         <v>56</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E113" t="s">
         <v>10</v>
       </c>
-      <c r="F113" s="1" t="s">
+      <c r="F113" t="s">
         <v>220</v>
       </c>
-      <c r="G113" s="1" t="str">
+      <c r="G113" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H113" s="1" t="str">
+      <c r="H113" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>205</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" t="s">
         <v>58</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" t="s">
         <v>19</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D114" t="s">
         <v>59</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E114" t="s">
         <v>24</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F114" t="s">
         <v>221</v>
       </c>
-      <c r="G114" s="1" t="str">
+      <c r="G114" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H114" s="1" t="str">
+      <c r="H114" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>205</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" t="s">
         <v>61</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" t="s">
         <v>19</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" t="s">
         <v>62</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E115" t="s">
         <v>24</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F115" t="s">
         <v>222</v>
       </c>
-      <c r="G115" s="1" t="str">
+      <c r="G115" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H115" s="1" t="str">
+      <c r="H115" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
+      <c r="A116" t="s">
         <v>205</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" t="s">
         <v>64</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" t="s">
         <v>19</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" t="s">
         <v>65</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E116" t="s">
         <v>10</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="F116" t="s">
         <v>223</v>
       </c>
-      <c r="G116" s="1" t="str">
+      <c r="G116" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H116" s="1" t="str">
+      <c r="H116" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
+      <c r="A117" t="s">
         <v>205</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" t="s">
         <v>67</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" t="s">
         <v>30</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D117" t="s">
         <v>68</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E117" t="s">
         <v>10</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F117" t="s">
         <v>224</v>
       </c>
-      <c r="G117" s="1" t="str">
+      <c r="G117" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H117" s="1" t="str">
+      <c r="H117" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+      <c r="A118" t="s">
         <v>205</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" t="s">
         <v>70</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" t="s">
         <v>30</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" t="s">
         <v>71</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E118" t="s">
         <v>10</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="F118" t="s">
         <v>225</v>
       </c>
-      <c r="G118" s="1" t="str">
+      <c r="G118" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H118" s="1" t="str">
+      <c r="H118" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
+      <c r="A119" t="s">
         <v>205</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" t="s">
         <v>73</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" t="s">
         <v>30</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" t="s">
         <v>74</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E119" t="s">
         <v>24</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F119" t="s">
         <v>226</v>
       </c>
-      <c r="G119" s="1" t="str">
+      <c r="G119" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H119" s="1" t="str">
+      <c r="H119" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
+      <c r="A120" t="s">
         <v>205</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" t="s">
         <v>76</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" t="s">
         <v>40</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D120" t="s">
         <v>77</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E120" t="s">
         <v>24</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="F120" t="s">
         <v>227</v>
       </c>
-      <c r="G120" s="1" t="str">
+      <c r="G120" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H120" s="1" t="str">
+      <c r="H120" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="1" t="s">
+      <c r="A121" t="s">
         <v>205</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" t="s">
         <v>79</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" t="s">
         <v>40</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" t="s">
         <v>80</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E121" t="s">
         <v>24</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="F121" t="s">
         <v>228</v>
       </c>
-      <c r="G121" s="1" t="str">
+      <c r="G121" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H121" s="1" t="str">
+      <c r="H121" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
+      <c r="A122" t="s">
         <v>205</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" t="s">
         <v>82</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" t="s">
         <v>40</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" t="s">
         <v>83</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E122" t="s">
         <v>24</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F122" t="s">
         <v>229</v>
       </c>
-      <c r="G122" s="1" t="str">
+      <c r="G122" t="str">
         <f t="shared" si="5"/>
         <v>ANG</v>
       </c>
-      <c r="H122" s="1" t="str">
+      <c r="H122" t="str">
         <f t="shared" si="4"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
+      <c r="A123" t="s">
         <v>205</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" t="s">
         <v>85</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" t="s">
         <v>8</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" t="s">
         <v>86</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E123" t="s">
         <v>24</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="F123" t="s">
         <v>230</v>
       </c>
-      <c r="G123" s="1" t="str">
+      <c r="G123" t="str">
         <f t="shared" si="5"/>
         <v>ESP</v>
       </c>
-      <c r="H123" s="1" t="str">
+      <c r="H123" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="1" t="s">
+      <c r="A124" t="s">
         <v>205</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" t="s">
         <v>88</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" t="s">
         <v>8</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D124" t="s">
         <v>89</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E124" t="s">
         <v>10</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="F124" t="s">
         <v>231</v>
       </c>
-      <c r="G124" s="1" t="str">
+      <c r="G124" t="str">
         <f t="shared" si="5"/>
         <v>ESP</v>
       </c>
-      <c r="H124" s="1" t="str">
+      <c r="H124" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="1" t="s">
+      <c r="A125" t="s">
         <v>205</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" t="s">
         <v>91</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" t="s">
         <v>8</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" t="s">
         <v>92</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E125" t="s">
         <v>10</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F125" t="s">
         <v>232</v>
       </c>
-      <c r="G125" s="1" t="str">
+      <c r="G125" t="str">
         <f t="shared" si="5"/>
         <v>ESP</v>
       </c>
-      <c r="H125" s="1" t="str">
+      <c r="H125" t="str">
         <f t="shared" si="4"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="1" t="s">
+      <c r="A126" t="s">
         <v>205</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" t="s">
         <v>94</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" t="s">
         <v>19</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" t="s">
         <v>95</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E126" t="s">
         <v>10</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F126" t="s">
         <v>233</v>
       </c>
-      <c r="G126" s="1" t="str">
+      <c r="G126" t="str">
         <f t="shared" si="5"/>
         <v>ESP</v>
       </c>
-      <c r="H126" s="1" t="str">
+      <c r="H126" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
+      <c r="A127" t="s">
         <v>205</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" t="s">
         <v>97</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" t="s">
         <v>19</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" t="s">
         <v>98</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E127" t="s">
         <v>10</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F127" t="s">
         <v>234</v>
       </c>
-      <c r="G127" s="1" t="str">
+      <c r="G127" t="str">
         <f t="shared" si="5"/>
         <v>ESP</v>
       </c>
-      <c r="H127" s="1" t="str">
+      <c r="H127" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
+      <c r="A128" t="s">
         <v>205</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" t="s">
         <v>100</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" t="s">
         <v>19</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" t="s">
         <v>101</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="E128" t="s">
         <v>10</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F128" t="s">
         <v>235</v>
       </c>
-      <c r="G128" s="1" t="str">
+      <c r="G128" t="str">
         <f t="shared" si="5"/>
         <v>ESP</v>
       </c>
-      <c r="H128" s="1" t="str">
+      <c r="H128" t="str">
         <f t="shared" si="4"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="1" t="s">
+      <c r="A129" t="s">
         <v>205</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B129" t="s">
         <v>103</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" t="s">
         <v>30</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" t="s">
         <v>104</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E129" t="s">
         <v>10</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F129" t="s">
         <v>236</v>
       </c>
-      <c r="G129" s="1" t="str">
+      <c r="G129" t="str">
         <f t="shared" si="5"/>
         <v>ESP</v>
       </c>
-      <c r="H129" s="1" t="str">
+      <c r="H129" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="1" t="s">
+      <c r="A130" t="s">
         <v>205</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" t="s">
         <v>106</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" t="s">
         <v>30</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" t="s">
         <v>107</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E130" t="s">
         <v>10</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F130" t="s">
         <v>237</v>
       </c>
-      <c r="G130" s="1" t="str">
+      <c r="G130" t="str">
         <f t="shared" ref="G130:G146" si="6">LEFT(B130,3)</f>
         <v>ESP</v>
       </c>
-      <c r="H130" s="1" t="str">
+      <c r="H130" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" s="1" t="s">
+      <c r="A131" t="s">
         <v>205</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B131" t="s">
         <v>109</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" t="s">
         <v>30</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" t="s">
         <v>110</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="E131" t="s">
         <v>10</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F131" t="s">
         <v>238</v>
       </c>
-      <c r="G131" s="1" t="str">
+      <c r="G131" t="str">
         <f t="shared" si="6"/>
         <v>ESP</v>
       </c>
-      <c r="H131" s="1" t="str">
+      <c r="H131" t="str">
         <f t="shared" si="4"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="1" t="s">
+      <c r="A132" t="s">
         <v>205</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B132" t="s">
         <v>112</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" t="s">
         <v>40</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" t="s">
         <v>113</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E132" t="s">
         <v>24</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F132" t="s">
         <v>239</v>
       </c>
-      <c r="G132" s="1" t="str">
+      <c r="G132" t="str">
         <f t="shared" si="6"/>
         <v>ESP</v>
       </c>
-      <c r="H132" s="1" t="str">
+      <c r="H132" t="str">
         <f t="shared" ref="H132:H146" si="7">MID(B132,5,3)</f>
         <v>OBF</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="1" t="s">
+      <c r="A133" t="s">
         <v>205</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" t="s">
         <v>115</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" t="s">
         <v>40</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" t="s">
         <v>116</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="E133" t="s">
         <v>24</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F133" t="s">
         <v>240</v>
       </c>
-      <c r="G133" s="1" t="str">
+      <c r="G133" t="str">
         <f t="shared" si="6"/>
         <v>ESP</v>
       </c>
-      <c r="H133" s="1" t="str">
+      <c r="H133" t="str">
         <f t="shared" si="7"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="1" t="s">
+      <c r="A134" t="s">
         <v>205</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" t="s">
         <v>117</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" t="s">
         <v>40</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" t="s">
         <v>118</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E134" t="s">
         <v>24</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F134" t="s">
         <v>241</v>
       </c>
-      <c r="G134" s="1" t="str">
+      <c r="G134" t="str">
         <f t="shared" si="6"/>
         <v>ESP</v>
       </c>
-      <c r="H134" s="1" t="str">
+      <c r="H134" t="str">
         <f t="shared" si="7"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
+      <c r="A135" t="s">
         <v>205</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B135" t="s">
         <v>120</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" t="s">
         <v>8</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" t="s">
         <v>121</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="E135" t="s">
         <v>10</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F135" t="s">
         <v>242</v>
       </c>
-      <c r="G135" s="1" t="str">
+      <c r="G135" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H135" s="1" t="str">
+      <c r="H135" t="str">
         <f t="shared" si="7"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A136" s="1" t="s">
+      <c r="A136" t="s">
         <v>205</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B136" t="s">
         <v>123</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" t="s">
         <v>8</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" t="s">
         <v>124</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="E136" t="s">
         <v>10</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F136" t="s">
         <v>243</v>
       </c>
-      <c r="G136" s="1" t="str">
+      <c r="G136" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H136" s="1" t="str">
+      <c r="H136" t="str">
         <f t="shared" si="7"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" s="1" t="s">
+      <c r="A137" t="s">
         <v>205</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B137" t="s">
         <v>126</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" t="s">
         <v>8</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" t="s">
         <v>127</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="E137" t="s">
         <v>10</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="F137" t="s">
         <v>244</v>
       </c>
-      <c r="G137" s="1" t="str">
+      <c r="G137" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H137" s="1" t="str">
+      <c r="H137" t="str">
         <f t="shared" si="7"/>
         <v>DIR</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" s="1" t="s">
+      <c r="A138" t="s">
         <v>205</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B138" t="s">
         <v>129</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C138" t="s">
         <v>19</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" t="s">
         <v>130</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="E138" t="s">
         <v>10</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F138" t="s">
         <v>245</v>
       </c>
-      <c r="G138" s="1" t="str">
+      <c r="G138" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H138" s="1" t="str">
+      <c r="H138" t="str">
         <f t="shared" si="7"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="1" t="s">
+      <c r="A139" t="s">
         <v>205</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" t="s">
         <v>132</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" t="s">
         <v>19</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D139" t="s">
         <v>133</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E139" t="s">
         <v>10</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F139" t="s">
         <v>246</v>
       </c>
-      <c r="G139" s="1" t="str">
+      <c r="G139" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H139" s="1" t="str">
+      <c r="H139" t="str">
         <f t="shared" si="7"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="1" t="s">
+      <c r="A140" t="s">
         <v>205</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B140" t="s">
         <v>135</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" t="s">
         <v>19</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="D140" t="s">
         <v>136</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="E140" t="s">
         <v>10</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="F140" t="s">
         <v>247</v>
       </c>
-      <c r="G140" s="1" t="str">
+      <c r="G140" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H140" s="1" t="str">
+      <c r="H140" t="str">
         <f t="shared" si="7"/>
         <v>ROL</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A141" s="1" t="s">
+      <c r="A141" t="s">
         <v>205</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" t="s">
         <v>138</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" t="s">
         <v>30</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" t="s">
         <v>139</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="E141" t="s">
         <v>10</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F141" t="s">
         <v>248</v>
       </c>
-      <c r="G141" s="1" t="str">
+      <c r="G141" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H141" s="1" t="str">
+      <c r="H141" t="str">
         <f t="shared" si="7"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A142" s="1" t="s">
+      <c r="A142" t="s">
         <v>205</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" t="s">
         <v>30</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" t="s">
         <v>142</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="E142" t="s">
         <v>10</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F142" t="s">
         <v>249</v>
       </c>
-      <c r="G142" s="1" t="str">
+      <c r="G142" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H142" s="1" t="str">
+      <c r="H142" t="str">
         <f t="shared" si="7"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A143" s="1" t="s">
+      <c r="A143" t="s">
         <v>205</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" t="s">
         <v>144</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C143" t="s">
         <v>30</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" t="s">
         <v>145</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="E143" t="s">
         <v>10</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="F143" t="s">
         <v>250</v>
       </c>
-      <c r="G143" s="1" t="str">
+      <c r="G143" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H143" s="1" t="str">
+      <c r="H143" t="str">
         <f t="shared" si="7"/>
         <v>LOG</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="s">
+      <c r="A144" t="s">
         <v>205</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" t="s">
         <v>147</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" t="s">
         <v>40</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" t="s">
         <v>148</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="E144" t="s">
         <v>10</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="F144" t="s">
         <v>251</v>
       </c>
-      <c r="G144" s="1" t="str">
+      <c r="G144" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H144" s="1" t="str">
+      <c r="H144" t="str">
         <f t="shared" si="7"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" s="1" t="s">
+      <c r="A145" t="s">
         <v>205</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" t="s">
         <v>150</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C145" t="s">
         <v>40</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D145" t="s">
         <v>151</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="E145" t="s">
         <v>10</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="F145" t="s">
         <v>252</v>
       </c>
-      <c r="G145" s="1" t="str">
+      <c r="G145" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H145" s="1" t="str">
+      <c r="H145" t="str">
         <f t="shared" si="7"/>
         <v>OBF</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="1" t="s">
+      <c r="A146" t="s">
         <v>205</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B146" t="s">
         <v>153</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C146" t="s">
         <v>40</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D146" t="s">
         <v>154</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="E146" t="s">
         <v>10</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="F146" t="s">
         <v>253</v>
       </c>
-      <c r="G146" s="1" t="str">
+      <c r="G146" t="str">
         <f t="shared" si="6"/>
         <v>SER</v>
       </c>
-      <c r="H146" s="1" t="str">
+      <c r="H146" t="str">
         <f t="shared" si="7"/>
         <v>OBF</v>
       </c>
